--- a/files/九龙-何文田-太子道西233号.xlsx
+++ b/files/九龙-何文田-太子道西233号.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="太子道西233号 销控表" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="太子道西233号" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,14 +44,19 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
       <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -63,7 +68,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00004D00"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -74,7 +79,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00002060"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -85,7 +90,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00660000"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -95,9 +100,30 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
       <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
     </font>
   </fonts>
   <fills count="9">
@@ -145,8 +171,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -176,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -193,19 +219,7 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -223,13 +237,37 @@
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -607,7 +645,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -4156,139 +4194,139 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>太子道西233号 - 太子道西233号 销控网格图</t>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>太子道西233号 销控网格图</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>总套数</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>在售 (Sale)</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>已定价未售</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>已售 (Sold)</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>暂停销售</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>待售 (Pending)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>75 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>5 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>70 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G4" s="19" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H4" s="19" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>A | 1748呎 (4+房)
 招标单位
@@ -4296,7 +4334,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>B | 1465呎 (4+房)
 招标单位
@@ -4304,422 +4342,422 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr"/>
-      <c r="E6" s="17" t="inlineStr"/>
-      <c r="F6" s="17" t="inlineStr"/>
-      <c r="G6" s="17" t="inlineStr"/>
-      <c r="H6" s="17" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="D5" s="21" t="inlineStr"/>
+      <c r="E5" s="21" t="inlineStr"/>
+      <c r="F5" s="21" t="inlineStr"/>
+      <c r="G5" s="21" t="inlineStr"/>
+      <c r="H5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>A | 1748呎 (4+房)
-$7,338万
+$7338万
 $41,979/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C7" s="18" t="inlineStr">
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t>B | 1530呎 (4+房)
-$6,378万
+$6378万
 $41,686/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr"/>
-      <c r="E7" s="17" t="inlineStr"/>
-      <c r="F7" s="17" t="inlineStr"/>
-      <c r="G7" s="17" t="inlineStr"/>
-      <c r="H7" s="17" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="D6" s="21" t="inlineStr"/>
+      <c r="E6" s="21" t="inlineStr"/>
+      <c r="F6" s="21" t="inlineStr"/>
+      <c r="G6" s="21" t="inlineStr"/>
+      <c r="H6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>A | 1039呎 (4+房)
-$3,117万
+$3117万
 $30,000/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>B | 1039呎 (4+房)
-$3,138万
+$3138万
 $30,202/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D8" s="18" t="inlineStr">
+      <c r="D7" s="22" t="inlineStr">
         <is>
           <t>C | 966呎 (4+房)
-$2,460万
+$2460万
 $25,466/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E8" s="18" t="inlineStr">
+      <c r="E7" s="22" t="inlineStr">
         <is>
           <t>D | 505呎 (2房)
-$1,240万
+$1240万
 $24,554/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F8" s="18" t="inlineStr">
+      <c r="F7" s="22" t="inlineStr">
         <is>
           <t>E | 971呎 (4+房)
-$2,750万
+$2750万
 $28,321/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G8" s="17" t="inlineStr"/>
-      <c r="H8" s="17" t="inlineStr"/>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B9" s="18" t="inlineStr">
+      <c r="G7" s="21" t="inlineStr"/>
+      <c r="H7" s="21" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>A | 1039呎 (4+房)
-$2,980万
+$2980万
 $28,681/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="C8" s="22" t="inlineStr">
         <is>
           <t>B | 1039呎 (4+房)
-$3,014万
+$3014万
 $29,010/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D9" s="18" t="inlineStr">
+      <c r="D8" s="22" t="inlineStr">
         <is>
           <t>C | 966呎 (4+房)
-$2,630万
+$2630万
 $27,226/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E9" s="18" t="inlineStr">
+      <c r="E8" s="22" t="inlineStr">
         <is>
           <t>D | 505呎 (2房)
-$1,225万
+$1225万
 $24,257/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F9" s="18" t="inlineStr">
+      <c r="F8" s="22" t="inlineStr">
         <is>
           <t>E | 971呎 (4+房)
-$2,631万
+$2631万
 $27,096/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G9" s="17" t="inlineStr"/>
-      <c r="H9" s="17" t="inlineStr"/>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="G8" s="21" t="inlineStr"/>
+      <c r="H8" s="21" t="inlineStr"/>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>A | 1039呎 (4+房)
-$2,947万
+$2947万
 $28,363/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t>B | 1039呎 (4+房)
-$2,650万
+$2650万
 $25,505/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D10" s="18" t="inlineStr">
+      <c r="D9" s="22" t="inlineStr">
         <is>
           <t>C | 966呎 (4+房)
-$2,283万
+$2283万
 $23,634/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E10" s="18" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t>D | 505呎 (2房)
-$1,215万
+$1215万
 $24,059/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F10" s="18" t="inlineStr">
+      <c r="F9" s="22" t="inlineStr">
         <is>
           <t>E | 971呎 (4+房)
-$2,588万
+$2588万
 $26,653/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G10" s="17" t="inlineStr"/>
-      <c r="H10" s="17" t="inlineStr"/>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="G9" s="21" t="inlineStr"/>
+      <c r="H9" s="21" t="inlineStr"/>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>A | 1039呎 (4+房)
-$2,920万
+$2920万
 $28,104/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr">
+      <c r="C10" s="22" t="inlineStr">
         <is>
           <t>B | 1039呎 (4+房)
-$2,863万
+$2863万
 $27,555/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D11" s="18" t="inlineStr">
+      <c r="D10" s="22" t="inlineStr">
         <is>
           <t>C | 966呎 (4+房)
-$2,570万
+$2570万
 $26,605/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E11" s="18" t="inlineStr">
+      <c r="E10" s="22" t="inlineStr">
         <is>
           <t>D | 505呎 (2房)
-$1,205万
+$1205万
 $23,861/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F11" s="18" t="inlineStr">
+      <c r="F10" s="22" t="inlineStr">
         <is>
           <t>E | 971呎 (4+房)
-$2,580万
+$2580万
 $26,571/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G11" s="17" t="inlineStr"/>
-      <c r="H11" s="17" t="inlineStr"/>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
+      <c r="G10" s="21" t="inlineStr"/>
+      <c r="H10" s="21" t="inlineStr"/>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
         <is>
           <t>A | 1039呎 (4+房)
-$2,849万
+$2849万
 $27,419/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C12" s="18" t="inlineStr">
+      <c r="C11" s="22" t="inlineStr">
         <is>
           <t>B | 1039呎 (4+房)
-$2,860万
+$2860万
 $27,526/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D12" s="18" t="inlineStr">
+      <c r="D11" s="22" t="inlineStr">
         <is>
           <t>C | 966呎 (4+房)
-$2,271万
+$2271万
 $23,509/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E12" s="18" t="inlineStr">
+      <c r="E11" s="22" t="inlineStr">
         <is>
           <t>D | 505呎 (2房)
-$1,198万
+$1198万
 $23,723/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F12" s="18" t="inlineStr">
+      <c r="F11" s="22" t="inlineStr">
         <is>
           <t>E | 971呎 (4+房)
-$2,268万
+$2268万
 $23,357/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G12" s="17" t="inlineStr"/>
-      <c r="H12" s="17" t="inlineStr"/>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
+      <c r="G11" s="21" t="inlineStr"/>
+      <c r="H11" s="21" t="inlineStr"/>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
         <is>
           <t>A | 1039呎 (4+房)
-$2,509万
+$2509万
 $24,146/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C13" s="18" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t>B | 1039呎 (4+房)
-$2,829万
+$2829万
 $27,226/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D13" s="18" t="inlineStr">
+      <c r="D12" s="22" t="inlineStr">
         <is>
           <t>C | 966呎 (4+房)
-$2,465万
+$2465万
 $25,518/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E13" s="18" t="inlineStr">
+      <c r="E12" s="22" t="inlineStr">
         <is>
           <t>D | 505呎 (2房)
-$1,183万
+$1183万
 $23,426/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F13" s="18" t="inlineStr">
+      <c r="F12" s="22" t="inlineStr">
         <is>
           <t>E | 971呎 (4+房)
-$2,275万
+$2275万
 $23,429/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G13" s="17" t="inlineStr"/>
-      <c r="H13" s="17" t="inlineStr"/>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
+      <c r="G12" s="21" t="inlineStr"/>
+      <c r="H12" s="21" t="inlineStr"/>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
         <is>
           <t>A | 1039呎 (4+房)
-$2,868万
+$2868万
 $27,603/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C14" s="18" t="inlineStr">
+      <c r="C13" s="22" t="inlineStr">
         <is>
           <t>B | 1039呎 (4+房)
-$2,850万
+$2850万
 $27,430/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D14" s="18" t="inlineStr">
+      <c r="D13" s="22" t="inlineStr">
         <is>
           <t>C | 966呎 (4+房)
-$2,582万
+$2582万
 $26,729/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E14" s="18" t="inlineStr">
+      <c r="E13" s="22" t="inlineStr">
         <is>
           <t>D | 505呎 (2房)
-$1,175万
+$1175万
 $23,267/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F14" s="18" t="inlineStr">
+      <c r="F13" s="22" t="inlineStr">
         <is>
           <t>E | 971呎 (4+房)
-$2,250万
+$2250万
 $23,172/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G14" s="17" t="inlineStr"/>
-      <c r="H14" s="17" t="inlineStr"/>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
+      <c r="G13" s="21" t="inlineStr"/>
+      <c r="H13" s="21" t="inlineStr"/>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
         <is>
           <t>A | 1039呎 (4+房)
-$2,500万
+$2500万
 $24,062/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C15" s="18" t="inlineStr">
+      <c r="C14" s="22" t="inlineStr">
         <is>
           <t>B | 1039呎 (4+房)
-$2,800万
+$2800万
 $26,949/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D15" s="18" t="inlineStr">
+      <c r="D14" s="22" t="inlineStr">
         <is>
           <t>C | 842呎 (3房)
-$1,866万
+$1866万
 $22,162/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E15" s="18" t="inlineStr">
+      <c r="E14" s="22" t="inlineStr">
         <is>
           <t>D | 668呎 (3房)
-$1,440万
+$1440万
 $21,557/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F15" s="16" t="inlineStr">
+      <c r="F14" s="20" t="inlineStr">
         <is>
           <t>E | 884呎 (3房)
 招标单位
@@ -4727,32 +4765,32 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G15" s="17" t="inlineStr"/>
-      <c r="H15" s="17" t="inlineStr"/>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
+      <c r="G14" s="21" t="inlineStr"/>
+      <c r="H14" s="21" t="inlineStr"/>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
         <is>
           <t>A | 1039呎 (4+房)
-$2,650万
+$2650万
 $25,505/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C16" s="18" t="inlineStr">
+      <c r="C15" s="22" t="inlineStr">
         <is>
           <t>B | 1039呎 (4+房)
-$2,410万
+$2410万
 $23,195/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D16" s="16" t="inlineStr">
+      <c r="D15" s="20" t="inlineStr">
         <is>
           <t>C | 842呎 (3房)
 招标单位
@@ -4760,64 +4798,64 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E16" s="18" t="inlineStr">
+      <c r="E15" s="22" t="inlineStr">
         <is>
           <t>D | 668呎 (3房)
-$1,410万
+$1410万
 $21,108/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F16" s="18" t="inlineStr">
+      <c r="F15" s="22" t="inlineStr">
         <is>
           <t>E | 884呎 (3房)
-$1,920万
+$1920万
 $21,719/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G16" s="17" t="inlineStr"/>
-      <c r="H16" s="17" t="inlineStr"/>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
+      <c r="G15" s="21" t="inlineStr"/>
+      <c r="H15" s="21" t="inlineStr"/>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
         <is>
           <t>A | 1039呎 (4+房)
-$2,435万
+$2435万
 $23,436/呎
 (24年-12月)</t>
         </is>
       </c>
-      <c r="C17" s="18" t="inlineStr">
+      <c r="C16" s="22" t="inlineStr">
         <is>
           <t>B | 1039呎 (4+房)
-$2,405万
+$2405万
 $23,147/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="D17" s="18" t="inlineStr">
+      <c r="D16" s="22" t="inlineStr">
         <is>
           <t>C | 842呎 (3房)
-$1,806万
+$1806万
 $21,449/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E17" s="18" t="inlineStr">
+      <c r="E16" s="22" t="inlineStr">
         <is>
           <t>D | 668呎 (3房)
-$1,435万
+$1435万
 $21,482/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F17" s="16" t="inlineStr">
+      <c r="F16" s="20" t="inlineStr">
         <is>
           <t>E | 884呎 (3房)
 招标单位
@@ -4825,24 +4863,24 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G17" s="17" t="inlineStr"/>
-      <c r="H17" s="17" t="inlineStr"/>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
+      <c r="G16" s="21" t="inlineStr"/>
+      <c r="H16" s="21" t="inlineStr"/>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
         <is>
           <t>A | 492呎 (2房)
-$1,107万
+$1107万
 $22,500/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C18" s="18" t="inlineStr">
+      <c r="C17" s="22" t="inlineStr">
         <is>
           <t>B | 376呎 (2房)
 $815万
@@ -4850,7 +4888,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D18" s="18" t="inlineStr">
+      <c r="D17" s="22" t="inlineStr">
         <is>
           <t>C | 375呎 (2房)
 $802万
@@ -4858,54 +4896,54 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E18" s="18" t="inlineStr">
+      <c r="E17" s="22" t="inlineStr">
         <is>
           <t>D | 495呎 (2房)
-$1,114万
+$1114万
 $22,500/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F18" s="18" t="inlineStr">
+      <c r="F17" s="22" t="inlineStr">
         <is>
           <t>E | 844呎 (3房)
-$1,755万
+$1755万
 $20,794/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G18" s="18" t="inlineStr">
+      <c r="G17" s="22" t="inlineStr">
         <is>
           <t>F | 668呎 (3房)
-$1,408万
+$1408万
 $21,078/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H18" s="18" t="inlineStr">
+      <c r="H17" s="22" t="inlineStr">
         <is>
           <t>G | 884呎 (3房)
-$1,822万
+$1822万
 $20,614/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
         <is>
           <t>A | 492呎 (2房)
-$1,059万
+$1059万
 $21,520/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C19" s="18" t="inlineStr">
+      <c r="C18" s="22" t="inlineStr">
         <is>
           <t>B | 376呎 (2房)
 $809万
@@ -4913,7 +4951,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D19" s="18" t="inlineStr">
+      <c r="D18" s="22" t="inlineStr">
         <is>
           <t>C | 375呎 (2房)
 $801万
@@ -4921,54 +4959,54 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E19" s="18" t="inlineStr">
+      <c r="E18" s="22" t="inlineStr">
         <is>
           <t>D | 495呎 (2房)
-$1,061万
+$1061万
 $21,434/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F19" s="18" t="inlineStr">
+      <c r="F18" s="22" t="inlineStr">
         <is>
           <t>E | 844呎 (3房)
-$1,750万
+$1750万
 $20,735/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G19" s="18" t="inlineStr">
+      <c r="G18" s="22" t="inlineStr">
         <is>
           <t>F | 668呎 (3房)
-$1,420万
+$1420万
 $21,257/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H19" s="18" t="inlineStr">
+      <c r="H18" s="22" t="inlineStr">
         <is>
           <t>G | 884呎 (3房)
-$1,818万
+$1818万
 $20,566/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
         <is>
           <t>A | 469呎 (2房)
-$1,027万
+$1027万
 $21,900/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C20" s="18" t="inlineStr">
+      <c r="C19" s="22" t="inlineStr">
         <is>
           <t>B | 376呎 (2房)
 $806万
@@ -4976,7 +5014,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D20" s="18" t="inlineStr">
+      <c r="D19" s="22" t="inlineStr">
         <is>
           <t>C | 375呎 (2房)
 $810万
@@ -4984,34 +5022,34 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E20" s="18" t="inlineStr">
+      <c r="E19" s="22" t="inlineStr">
         <is>
           <t>D | 473呎 (2房)
-$1,025万
+$1025万
 $21,671/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F20" s="18" t="inlineStr">
+      <c r="F19" s="22" t="inlineStr">
         <is>
           <t>E | 809呎 (3房)
-$1,783万
+$1783万
 $22,040/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G20" s="18" t="inlineStr">
+      <c r="G19" s="22" t="inlineStr">
         <is>
           <t>F | 636呎 (3房)
-$1,396万
+$1396万
 $21,954/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H20" s="18" t="inlineStr">
+      <c r="H19" s="22" t="inlineStr">
         <is>
           <t>G | 849呎 (3房)
-$2,290万
+$2290万
 $26,973/呎
 (已售)</t>
         </is>
@@ -5019,7 +5057,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
